--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00722B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00722B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2E19081-C98C-456B-84DC-A33414EC9321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{902BAA33-E28B-4F30-90F0-8BB41D31D9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{84AC7B9E-9F9C-42AA-9677-5D45179B96BC}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{6FA6B648-D2D7-400D-AAEC-D5E390D59343}"/>
   </bookViews>
   <sheets>
     <sheet name="00722B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1633,25 +1633,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84240AB2-F87A-4AA6-9A51-4C2588EB857B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D439D3FF-942F-4B94-B3E7-990CAC0D36BC}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1805,7 +1805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1885,7 +1885,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2018</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>27</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>27</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="49" t="s">
         <v>82</v>
       </c>
